--- a/examples/hello-table/fixtures/finance.msoffice-resaved.xlsx
+++ b/examples/hello-table/fixtures/finance.msoffice-resaved.xlsx
@@ -16,11 +16,11 @@
     <sheet name="Q3" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000011" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000011">'Q3'!$A$1</definedName>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
-    <definedName name="ox_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
-    <definedName name="ox_revision">"3b0b95b52b828de91bcdb13f"</definedName>
-    <definedName name="ox_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000011" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000011">'Q3'!$A$1</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
+    <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
+    <definedName name="mleaf_revision">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName name="mleaf_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/examples/hello-table/fixtures/finance.msoffice-resaved.xlsx
+++ b/examples/hello-table/fixtures/finance.msoffice-resaved.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/examples/hello-table/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="~/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7622A2BA-3805-4249-BEA3-5BCE9655AAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF4DE75F-7BB4-9242-8515-BFB306511E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="34560" windowHeight="22340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Q3" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000011" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000011">'Q3'!$A$1</definedName>
     <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000012">'Q3'!$A$1:$B$4</definedName>
     <definedName name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" comment="milleleaf node 3f1c2a90-0000-4c1e-9a00-000000000013">'Q3'!$B$5</definedName>
-    <definedName name="mleaf_revision">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName name="mleaf_revision">"c50ea0fe36a3631b2dbab632"</definedName>
     <definedName name="mleaf_workbook">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
